--- a/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0001T0006Z000C1N37_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0001T0006Z000C1N37_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>18.01835613269146</v>
+        <v>2.927982871562363</v>
       </c>
       <c r="D2" t="n">
-        <v>17.15076925980049</v>
+        <v>2.787000004717579</v>
       </c>
       <c r="E2" t="n">
-        <v>10.64396848065542</v>
+        <v>1.729644878106506</v>
       </c>
       <c r="F2" t="n">
-        <v>10.81506726113765</v>
+        <v>1.757448429934868</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>10.71935829356345</v>
+        <v>1.741895722704061</v>
       </c>
       <c r="D3" t="n">
-        <v>9.964860220218013</v>
+        <v>1.619289785785427</v>
       </c>
       <c r="E3" t="n">
-        <v>10.64396848065542</v>
+        <v>1.729644878106506</v>
       </c>
       <c r="F3" t="n">
-        <v>10.81506726113765</v>
+        <v>1.757448429934868</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>41.39017597062568</v>
+        <v>6.725903595226673</v>
       </c>
       <c r="D4" t="n">
-        <v>41.0908455026064</v>
+        <v>6.67726239417354</v>
       </c>
       <c r="E4" t="n">
-        <v>10.64396848065542</v>
+        <v>1.729644878106506</v>
       </c>
       <c r="F4" t="n">
-        <v>10.81506726113765</v>
+        <v>1.757448429934868</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>15.9581472877675</v>
+        <v>2.593198934262218</v>
       </c>
       <c r="D5" t="n">
-        <v>15.38943197883874</v>
+        <v>2.500782696561295</v>
       </c>
       <c r="E5" t="n">
-        <v>10.64396848065542</v>
+        <v>1.729644878106506</v>
       </c>
       <c r="F5" t="n">
-        <v>10.81506726113765</v>
+        <v>1.757448429934868</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>25.36157199533727</v>
+        <v>4.121255449242306</v>
       </c>
       <c r="D6" t="n">
-        <v>24.95449587025306</v>
+        <v>4.055105578916122</v>
       </c>
       <c r="E6" t="n">
-        <v>10.64396848065542</v>
+        <v>1.729644878106506</v>
       </c>
       <c r="F6" t="n">
-        <v>10.81506726113765</v>
+        <v>1.757448429934868</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
